--- a/static/dataset/mps_metadata.xlsx
+++ b/static/dataset/mps_metadata.xlsx
@@ -25,7 +25,7 @@
     <t>Constituency</t>
   </si>
   <si>
-    <t>Section_Name</t>
+    <t>Session_Name</t>
   </si>
   <si>
     <t>Days_Attended</t>

--- a/static/dataset/mps_metadata.xlsx
+++ b/static/dataset/mps_metadata.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
   <si>
     <t>MP_Name</t>
   </si>
@@ -61,10 +61,22 @@
     <t>Rajya Sabha</t>
   </si>
   <si>
-    <t>Karnataka</t>
-  </si>
-  <si>
-    <t>N/A</t>
+    <t>Kerala</t>
+  </si>
+  <si>
+    <t>kottayam</t>
+  </si>
+  <si>
+    <t>Suresh Gopi</t>
+  </si>
+  <si>
+    <t>Thrissur</t>
+  </si>
+  <si>
+    <t>17th LS - Winter 2023</t>
+  </si>
+  <si>
+    <t>17th LS - WInter 2023</t>
   </si>
 </sst>
 </file>
@@ -415,6 +427,64 @@
         <v>4.0</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="I5" s="1">
+        <v>6.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
